--- a/ig/DM-JUILLET-2026/ValueSet-jdv-section-document-cisis.xlsx
+++ b/ig/DM-JUILLET-2026/ValueSet-jdv-section-document-cisis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="281">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260619134042</t>
+    <t>20260716085852</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:40:42+01:00</t>
+    <t>2026-07-16T08:58:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -846,12 +846,6 @@
   </si>
   <si>
     <t>Résultats de laboratoire scannés</t>
-  </si>
-  <si>
-    <t>xx-MCH-PsychoMDev</t>
-  </si>
-  <si>
-    <t>Développement psychomoteur</t>
   </si>
   <si>
     <t>http://loinc.org</t>
@@ -1181,7 +1175,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B125"/>
+  <dimension ref="A1:B124"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2166,26 +2160,18 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>277</v>
+        <v>32</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>278</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -2212,10 +2198,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3">
@@ -2231,7 +2217,7 @@
         <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
